--- a/results/job_matches_2026-09-04.xlsx
+++ b/results/job_matches_2026-09-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>^Data Engineer - 6461115</t>
+          <t>1000000882.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a74613dbe565650</t>
+          <t>https://www.indeed.com/viewjob?jk=7843267cf992ea15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>1000000881.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d327cf6aabca3bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a34457b20435ae3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Developer with AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, EMR, Azure, Google Cloud Platform, Dataflow, HBase, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c9639c442911cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad70f5252874459</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Indicium AI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5bcfb63295905b</t>
+          <t>https://www.indeed.com/viewjob?jk=72cc11f621d19b31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Database Engineer &amp; Developer, Security Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f700b926bc75474</t>
+          <t>https://www.indeed.com/viewjob?jk=bcff22cb22d06c48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Data Engineer - Houston</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Indicium AI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e249f1007751107</t>
+          <t>https://www.indeed.com/viewjob?jk=81609495aaa654a3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Cloud Data Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, SQS, RDS, Azure, Databricks, Event Hubs, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279b005ffce20271</t>
+          <t>https://www.indeed.com/viewjob?jk=f362c9602042b5aa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1000000882.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7843267cf992ea15</t>
+          <t>https://www.indeed.com/viewjob?jk=fb65efe8a988bc77</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1000000881.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
+          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a34457b20435ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Developer with AI</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Google Cloud Platform, Dataflow, HBase, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad70f5252874459</t>
+          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MLOps &amp; Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sierra Nevada Corporation</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lone Tree, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d119b132aefd5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer Consultant</t>
+          <t>Sr. Software Engineer - AI Quality and Productivity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indicium AI</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cc11f621d19b31</t>
+          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer &amp; Developer, Security Data</t>
+          <t>Full Stack Engineer (Java)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcff22cb22d06c48</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7a912adddfab10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer - Houston</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indicium AI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81609495aaa654a3</t>
+          <t>https://www.indeed.com/viewjob?jk=189bcc446c9dab44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e7624bacd3c7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c366764337f1ed92</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f362c9602042b5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6058b9b613bca110</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb65efe8a988bc77</t>
+          <t>https://www.indeed.com/viewjob?jk=44f312befe7b6228</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fabric Architect</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c4ffa6f4022338</t>
+          <t>https://www.indeed.com/viewjob?jk=825ced6b050f62ff</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b2962748d9789</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,172 +1196,172 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=62e526d781156add</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
+          <t>https://www.indeed.com/viewjob?jk=bf99c34ea81acf0e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer (Hybrid)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29dcd9067394b82</t>
+          <t>https://www.indeed.com/viewjob?jk=97bedc8e0921c527</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Java)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7a912adddfab10</t>
+          <t>https://www.indeed.com/viewjob?jk=f053a808a64ce63c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74016e8b1c1cf6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2234682221b2376</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5468b9bf305c96</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9ca1626e817a0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Team Center PLM Architect</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>E-solutions Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf50044bf3b2178</t>
+          <t>https://www.indeed.com/viewjob?jk=742f43f81b2c60f7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,15 +1458,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b602f77b928622</t>
+          <t>https://www.indeed.com/viewjob?jk=2401405eb3baa60e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,15 +1493,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a58bed0c2d1c26</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2850791f386fd0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,15 +1528,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e381d6a5f4918a</t>
+          <t>https://www.indeed.com/viewjob?jk=745d572a1734deb3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,15 +1563,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2928f8de05a5880f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5bd5047cb690b7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,15 +1598,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59c0167102920ff0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c9d895b4b221fc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,15 +1633,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd92748e7a09744</t>
+          <t>https://www.indeed.com/viewjob?jk=6f901d63ec543ec6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,15 +1668,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3e74cdf07bf5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a2c68b1f9879c6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,15 +1703,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3891bf419843c06e</t>
+          <t>https://www.indeed.com/viewjob?jk=86fa80072663c39c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,15 +1738,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfba9c82293ef7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=34cfdf03756d098f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,15 +1773,15 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9554b027ea016221</t>
+          <t>https://www.indeed.com/viewjob?jk=34becb3bb737a3a8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,15 +1808,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151ab6f759331e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=40c481cde165be31</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,15 +1843,15 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5e0807495bc5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1deaba387bdf2e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,15 +1878,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425e768e43b69bff</t>
+          <t>https://www.indeed.com/viewjob?jk=db635ff6ebf1d5ba</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,15 +1913,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e293e334c27ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4df6e348da45185</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,15 +1948,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e6b189059b3dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d3246b068fda8b24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>System Engineer, Data Automation and AI</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=01a11e4dca1338bd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
+          <t>https://www.indeed.com/viewjob?jk=6493bf4f59fe501c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
+          <t>https://www.indeed.com/viewjob?jk=19cafaf0905d6ccd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 2 – Austin, TX (Hybrid)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Startekk Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efae37094a72458c</t>
+          <t>https://www.indeed.com/viewjob?jk=d179f64661459840</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e187ddd5c7b1c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b3b4996f2df17d3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c14c404355ce78</t>
+          <t>https://www.indeed.com/viewjob?jk=c769c3d835ff3db7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
+          <t>https://www.indeed.com/viewjob?jk=927f4de3ddcabe55</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
+          <t>https://www.indeed.com/viewjob?jk=55c467b89913b40c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=97f79742bd18fbf9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Infrastructure and DevOps Architect</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01dfa6d358650f</t>
+          <t>https://www.indeed.com/viewjob?jk=48534502200da502</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e889fa62a0aa04</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ce4e192219a234</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I – SRE</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c386ab65035eb143</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Customer AI Analytics</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
+          <t>https://www.indeed.com/viewjob?jk=04781ba0e218324c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=38959fe002eaa620</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a45ce59fb7c995</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9152e708942be7c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e237f57d26686583</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
+          <t>https://www.indeed.com/viewjob?jk=1d50878a49c11777</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
+          <t>https://www.indeed.com/viewjob?jk=9c332f08ebbb5911</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>DataBricks Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Sr. Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=f91a79069b7b6c23</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>System Engineer, Data Automation and AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
+          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Cloud Solutions Architect 2 – Austin, TX (Hybrid)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Startekk Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
+          <t>https://www.indeed.com/viewjob?jk=efae37094a72458c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Integration Developer - API Platform</t>
+          <t>Cashier</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Viet Crispwich</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38d53eb67f89550</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0954321572d7e1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,89 +3051,89 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
+          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Infrastructure and DevOps Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01dfa6d358650f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
+          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3142,81 +3142,81 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
+          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
+          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
+          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>International Community Health Services</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>EMR, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f087a7f276c81325</t>
+          <t>https://www.indeed.com/viewjob?jk=21fdae74ac4398f4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Ops Engineer I – SRE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Cyber Security Engineer - Automation</t>
+          <t>Senior Data Engineer – Customer AI Analytics</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd974acb38b1c48</t>
+          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
+          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
+          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9e283de70978e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
+          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
+          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer III</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
+          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Developer - AI</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c7307c5a0e8d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medina Talent Group </t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
+          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer - Remote</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,102 +3786,102 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Sourceo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>Azure, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
+          <t>https://www.indeed.com/viewjob?jk=a95571cda13f4ac4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
+          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer - Automation</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bdadf15bcddb227</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JobSiteCare</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53647361cafcb4a7</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Backend)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,54 +3996,54 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ITSM Service Now Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
+          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4052,11 +4052,11 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
+          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DevSecOps Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9dc833901dbedff</t>
+          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51906ecf9dea52d</t>
+          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfe24562dfa1c33</t>
+          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Scala, Kafka, PostgreSQL, Data Modeling, ETL, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,102 +4206,102 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c52ac26fe3b63f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9e283de70978e9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI-Enabled Data Architecture Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bannockburn, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
+          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Marketplace</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
+          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t xml:space="preserve">Medina Talent Group </t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Platform Engineer - Remote</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. FSE Engineer (Java/Python)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
+          <t>https://www.indeed.com/viewjob?jk=5260c6496b06df56</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Paradox Machines</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>Rakuten International</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
+          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Security Engineer - Automation</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
+          <t>https://www.indeed.com/viewjob?jk=0bdadf15bcddb227</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>University of Tennessee Health Science Center</t>
+          <t>JobSiteCare</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
+          <t>https://www.indeed.com/viewjob?jk=53647361cafcb4a7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
+          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>University of Tennessee</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,137 +4591,137 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
+          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer (Data Backend)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>In-N-Out Burger</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
+          <t>Frontend Architect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Greater Anesthesia Solutions</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
+          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
+          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Frontend Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a7f97444948657</t>
+          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>DevSecOps Architect</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cf49ee0837de3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9dc833901dbedff</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Context Layer Engineer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
+          <t>https://www.indeed.com/viewjob?jk=b51906ecf9dea52d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Context Layer Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
+          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>.Net developer (strong Azure)</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Stier Solutions Inc</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=acfe24562dfa1c33</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
+          <t>Senior Software Engineer - ITSM Service Now Team</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,17 +4896,682 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Modus Create</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CREDIT GENIE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CREDIT GENIE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CREDIT GENIE</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Paradox Machines</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Infinity</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Everseen</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>University of Tennessee Health Science Center</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>University of Tennessee</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>In-N-Out Burger</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Greater Anesthesia Solutions</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Data Architect - Snowflake &amp; AWS</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>J2B GLOBAL LLC</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, IAM, Scala, Snowflake, Data Modeling, Terraform, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7be41efb52cec9d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Cloud Data Architect</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93a7f97444948657</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55cf49ee0837de3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Context Layer Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>.Net developer (strong Azure)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Stier Solutions Inc</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Sherwin-Williams</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Context Layer Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer III</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=811249074303b1b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>NAVA TECH LLC</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Data Modeling, ETL, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66b1fb657f32bd19</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-04.xlsx
+++ b/results/job_matches_2026-09-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,60 +643,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer &amp; Developer, Security Data</t>
+          <t>Forward Deployed Data Engineer - Houston</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Indicium AI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcff22cb22d06c48</t>
+          <t>https://www.indeed.com/viewjob?jk=81609495aaa654a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer - Houston</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Indicium AI</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81609495aaa654a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f362c9602042b5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
         </is>
       </c>
     </row>
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb65efe8a988bc77</t>
+          <t>https://www.indeed.com/viewjob?jk=f362c9602042b5aa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb65efe8a988bc77</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
+          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Quality and Productivity</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
+          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Java)</t>
+          <t>Sr. Software Engineer - AI Quality and Productivity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7a912adddfab10</t>
+          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189bcc446c9dab44</t>
+          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>DataBricks Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c366764337f1ed92</t>
+          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6058b9b613bca110</t>
+          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Technical Architect - Boomi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f312befe7b6228</t>
+          <t>https://www.indeed.com/viewjob?jk=b63dd269336a90eb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Boomi Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825ced6b050f62ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a701b23e34d3c27b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Full Stack Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b2962748d9789</t>
+          <t>https://www.indeed.com/viewjob?jk=f91a79069b7b6c23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e526d781156add</t>
+          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>System Engineer, Data Automation and AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf99c34ea81acf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97bedc8e0921c527</t>
+          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Systems Analyst - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Rialto Capital</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f053a808a64ce63c</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe46512a7712cf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Cloud Solutions Architect 2 – Austin, TX (Hybrid)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Startekk Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2234682221b2376</t>
+          <t>https://www.indeed.com/viewjob?jk=efae37094a72458c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5468b9bf305c96</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Cashier</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Viet Crispwich</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9ca1626e817a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0954321572d7e1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=742f43f81b2c60f7</t>
+          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2401405eb3baa60e</t>
+          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2850791f386fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Infrastructure and DevOps Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745d572a1734deb3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01dfa6d358650f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5bd5047cb690b7</t>
+          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c9d895b4b221fc</t>
+          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f901d63ec543ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a2c68b1f9879c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>International Community Health Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>EMR, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fa80072663c39c</t>
+          <t>https://www.indeed.com/viewjob?jk=21fdae74ac4398f4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Cloud Ops Engineer I – SRE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34cfdf03756d098f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer – Customer AI Analytics</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34becb3bb737a3a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c481cde165be31</t>
+          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1deaba387bdf2e</t>
+          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db635ff6ebf1d5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4df6e348da45185</t>
+          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3246b068fda8b24</t>
+          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a11e4dca1338bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6493bf4f59fe501c</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cafaf0905d6ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d179f64661459840</t>
+          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b3b4996f2df17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c769c3d835ff3db7</t>
+          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927f4de3ddcabe55</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c467b89913b40c</t>
+          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f79742bd18fbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48534502200da502</t>
+          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ce4e192219a234</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c386ab65035eb143</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04781ba0e218324c</t>
+          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38959fe002eaa620</t>
+          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a45ce59fb7c995</t>
+          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9152e708942be7c</t>
+          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e237f57d26686583</t>
+          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d50878a49c11777</t>
+          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Developer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, GCP, Vertex AI, Scala, Kafka, MongoDB</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c332f08ebbb5911</t>
+          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DataBricks Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t xml:space="preserve">Medina Talent Group </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
+          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Platform Engineer - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Developer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91a79069b7b6c23</t>
+          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
+          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>System Engineer, Data Automation and AI</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Rakuten Global</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Sr. FSE Engineer (Java/Python)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
+          <t>https://www.indeed.com/viewjob?jk=5260c6496b06df56</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 2 – Austin, TX (Hybrid)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Startekk Inc</t>
+          <t>Rakuten International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efae37094a72458c</t>
+          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
+          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Viet Crispwich</t>
+          <t>JobSiteCare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0954321572d7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=53647361cafcb4a7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer (Data Backend)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
+          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Frontend Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Frontend Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Infrastructure and DevOps Architect</t>
+          <t>DevSecOps Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01dfa6d358650f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9dc833901dbedff</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
+          <t>https://www.indeed.com/viewjob?jk=b51906ecf9dea52d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
+          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Software Engineer - ITSM Service Now Team</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
+          <t>https://www.indeed.com/viewjob?jk=acfe24562dfa1c33</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Backend Engineer, IoT Architecture &amp; Migration</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>International Community Health Services</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>EMR, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fdae74ac4398f4</t>
+          <t>https://www.indeed.com/viewjob?jk=428d030a371efde6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I – SRE</t>
+          <t>Infrastructure Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Customer AI Analytics</t>
+          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,19 +3401,19 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3422,11 +3422,11 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Data Engineer - Paradox Machines</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Infinity</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
+          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>University of Tennessee Health Science Center</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>University of Tennessee</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Greater Anesthesia Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Data Architect - Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Scala, Snowflake, Data Modeling, Terraform, CloudWatch</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=7be41efb52cec9d7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
+          <t>https://www.indeed.com/viewjob?jk=93a7f97444948657</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>.Net developer (strong Azure)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Stier Solutions Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Context Layer Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Context Layer Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sourceo</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Event Hubs, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95571cda13f4ac4</t>
+          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=e198e6ac2972e7f1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,1650 +3926,40 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=306f0bd44cd0eb2d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>WhiteWater Express Car Wash</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Appleton, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Enterprise ServiceNow Architect</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Enterprise Data Architect</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>AI Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Cencora</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Kafka Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>American Electric Power</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9e283de70978e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medina Talent Group </t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Cloud Data Platform Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Highlights for Children</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Sr. FSE Engineer (Java/Python)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5260c6496b06df56</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Rakuten International</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Cyber Security Engineer - Automation</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Versant</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bdadf15bcddb227</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior .NET Developer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>JobSiteCare</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53647361cafcb4a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Data Backend)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Steerbridge</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Frontend Architect</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Molex</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Frontend Architect</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Molex</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Lisle, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>DevSecOps Architect</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Hard Rock International</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Davie, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9dc833901dbedff</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Architect</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Birlasoft</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b51906ecf9dea52d</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Associate Actuary</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Wildfire Defense Systems</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Bozeman, MT, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acfe24562dfa1c33</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - ITSM Service Now Team</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Fort Washington, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Modus Create</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Modus Create</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Paradox Machines</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Infinity</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Everseen</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>University of Tennessee Health Science Center</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>University of Tennessee</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>In-N-Out Burger</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Greater Anesthesia Solutions</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Data Architect - Snowflake &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>J2B GLOBAL LLC</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Scala, Snowflake, Data Modeling, Terraform, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7be41efb52cec9d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Cloud Data Architect</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93a7f97444948657</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior .NET Developer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55cf49ee0837de3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Context Layer Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>.Net developer (strong Azure)</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Stier Solutions Inc</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Sherwin-Williams</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Context Layer Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=811249074303b1b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>NAVA TECH LLC</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Data Modeling, ETL, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=66b1fb657f32bd19</t>
         </is>

--- a/results/job_matches_2026-09-04.xlsx
+++ b/results/job_matches_2026-09-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,52 +818,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
+          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Quality and Productivity</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
+          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer - AI Quality and Productivity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DataBricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
+          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DataBricks Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technical Architect - Boomi</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63dd269336a90eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Boomi Engineer - Senior Consultant</t>
+          <t>Technical Architect - Boomi</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a701b23e34d3c27b</t>
+          <t>https://www.indeed.com/viewjob?jk=b63dd269336a90eb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Developer</t>
+          <t>Boomi Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91a79069b7b6c23</t>
+          <t>https://www.indeed.com/viewjob?jk=a701b23e34d3c27b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Full Stack Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
+          <t>https://www.indeed.com/viewjob?jk=f91a79069b7b6c23</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>System Engineer, Data Automation and AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>System Engineer, Data Automation and AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
+          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Systems Analyst - Remote</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rialto Capital</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe46512a7712cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 2 – Austin, TX (Hybrid)</t>
+          <t>Systems Analyst - Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Startekk Inc</t>
+          <t>Rialto Capital</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efae37094a72458c</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe46512a7712cf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Cloud Solutions Architect 2 – Austin, TX (Hybrid)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Startekk Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
+          <t>https://www.indeed.com/viewjob?jk=efae37094a72458c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Viet Crispwich</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0954321572d7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cashier</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Viet Crispwich</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0954321572d7e1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Infrastructure and DevOps Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01dfa6d358650f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure and DevOps Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01dfa6d358650f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Databricks Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
+          <t>https://www.indeed.com/viewjob?jk=323ab8f6158c9d11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
+          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
+          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>International Community Health Services</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EMR, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fdae74ac4398f4</t>
+          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I – SRE</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Customer AI Analytics</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>International Community Health Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>EMR, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
+          <t>https://www.indeed.com/viewjob?jk=21fdae74ac4398f4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Cloud Ops Engineer I – SRE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Data Engineer – Customer AI Analytics</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
+          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
+          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
+          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
+          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
+          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,24 +2446,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
+          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
+          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
+          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
+          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t xml:space="preserve">Medina Talent Group </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Data Platform Engineer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medina Talent Group </t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer - Remote</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
+          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Rakuten Global</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr. FSE Engineer (Java/Python)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rakuten Global</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=5260c6496b06df56</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. FSE Engineer (Java/Python)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Rakuten International</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5260c6496b06df56</t>
+          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Rakuten International</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
+          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
+          <t>BI DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Temco Logistics</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Carson, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
+          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Senior Software Engineer (Data Backend)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JobSiteCare</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53647361cafcb4a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Backend)</t>
+          <t>Frontend Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
+          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
+          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Frontend Architect</t>
+          <t>DevSecOps Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
+          <t>https://www.indeed.com/viewjob?jk=a9dc833901dbedff</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevSecOps Architect</t>
+          <t>AI Engineer - Direct Hire Only, no Corp-2-Corp</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Pistevo Decision</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9dc833901dbedff</t>
+          <t>https://www.indeed.com/viewjob?jk=b60fbf6be4c551ad</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51906ecf9dea52d</t>
+          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - ITSM Service Now Team</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ITSM Service Now Team</t>
+          <t>Associate, Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
+          <t>Scala, Kafka, PostgreSQL, Data Modeling, ETL, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
+          <t>https://www.indeed.com/viewjob?jk=61c52ac26fe3b63f</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (DevOps)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Infrastructure Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
+          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
+          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Paradox Machines</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Paradox Machines</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Infinity</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
+          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>University of Tennessee Health Science Center</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
+          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>University of Tennessee</t>
+          <t>University of Tennessee Health Science Center</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Greater Anesthesia Solutions</t>
+          <t>University of Tennessee</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
+          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect - Snowflake &amp; AWS</t>
+          <t>AWS Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Scala, Snowflake, Data Modeling, Terraform, CloudWatch</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be41efb52cec9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a7f97444948657</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>.Net developer (strong Azure)</t>
+          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Stier Solutions Inc</t>
+          <t>Greater Anesthesia Solutions</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
+          <t>Data Architect - Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Scala, Snowflake, Data Modeling, Terraform, CloudWatch</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
+          <t>https://www.indeed.com/viewjob?jk=7be41efb52cec9d7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Context Layer Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
+          <t>https://www.indeed.com/viewjob?jk=93a7f97444948657</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Context Layer Engineer</t>
+          <t>.Net developer (strong Azure)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Stier Solutions Inc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e198e6ac2972e7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Context Layer Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306f0bd44cd0eb2d</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Context Layer Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,15 +3951,120 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer III</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e198e6ac2972e7f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer III</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=306f0bd44cd0eb2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NAVA TECH LLC</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=66b1fb657f32bd19</t>
         </is>

--- a/results/job_matches_2026-09-04.xlsx
+++ b/results/job_matches_2026-09-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>^Data Engineer - 6461115</t>
+          <t>1000000882.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a6fe2dd4415dd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=7843267cf992ea15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1000000882.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
+          <t>1000000881.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7843267cf992ea15</t>
+          <t>https://www.indeed.com/viewjob?jk=1a34457b20435ae3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1000000881.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
+          <t>Java Developer with AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Azure, Google Cloud Platform, Dataflow, HBase, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a34457b20435ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad70f5252874459</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Developer with AI</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Google Cloud Platform, Dataflow, HBase, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad70f5252874459</t>
+          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer Consultant</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Indicium AI</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cc11f621d19b31</t>
+          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer - Houston</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Indicium AI</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81609495aaa654a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f362c9602042b5aa</t>
         </is>
       </c>
     </row>
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb65efe8a988bc77</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
+          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f362c9602042b5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb65efe8a988bc77</t>
+          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Sr. Software Engineer - AI Quality and Productivity</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
+          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,94 +916,94 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>DataBricks Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Quality and Productivity</t>
+          <t>Technical Architect - Boomi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
+          <t>https://www.indeed.com/viewjob?jk=b63dd269336a90eb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Boomi Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a701b23e34d3c27b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DataBricks Data Engineer</t>
+          <t>Sr. Full Stack Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
+          <t>https://www.indeed.com/viewjob?jk=f91a79069b7b6c23</t>
         </is>
       </c>
     </row>
@@ -1068,20 +1068,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,129 +1091,129 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Technical Architect - Boomi</t>
+          <t>System Engineer, Data Automation and AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63dd269336a90eb</t>
+          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Boomi Engineer - Senior Consultant</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a701b23e34d3c27b</t>
+          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Developer</t>
+          <t>Systems Analyst - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Rialto Capital</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91a79069b7b6c23</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe46512a7712cf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
+          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>System Engineer, Data Automation and AI</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
+          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Systems Analyst - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rialto Capital</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe46512a7712cf</t>
+          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 2 – Austin, TX (Hybrid)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Startekk Inc</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efae37094a72458c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Databricks Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=323ab8f6158c9d11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
+          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Viet Crispwich</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0954321572d7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9668a782d26f23f2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
+          <t>https://www.indeed.com/viewjob?jk=c80fb7f5a0962d33</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Infrastructure and DevOps Architect</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01dfa6d358650f</t>
+          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Databricks Architect (Onsite Hybrid)</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323ab8f6158c9d11</t>
+          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>International Community Health Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>EMR, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
+          <t>https://www.indeed.com/viewjob?jk=21fdae74ac4398f4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Cloud Ops Engineer I – SRE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Data Engineer – Customer AI Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
+          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,77 +1746,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
+          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>International Community Health Services</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EMR, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fdae74ac4398f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a599be99d023bcc4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I – SRE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Customer AI Analytics</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,137 +2001,137 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Data Engineer, Payment Data Intelligence</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
+          <t>https://www.indeed.com/viewjob?jk=95f8298a7d1edc2e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Data Engineer - Office-Based in Minnesota</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
+          <t>https://www.indeed.com/viewjob?jk=f8abd386f3997679</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a155cddb69c0b0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t xml:space="preserve">Medina Talent Group </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Rakuten Global</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Rakuten International</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
+          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>BI DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Temco Logistics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carson, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
+          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
+          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
+          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Senior Software Engineer (Data Backend)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,172 +2456,172 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
+          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Frontend Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
+          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Frontend Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
+          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
+          <t>Sr. Analyst, Supply Chain Data Analytics</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Newell Brands</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer - Direct Hire Only, no Corp-2-Corp</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Pistevo Decision</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b60fbf6be4c551ad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer - ITSM Service Now Team</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medina Talent Group </t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
+          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Associate, Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
+          <t>Scala, Kafka, PostgreSQL, Data Modeling, ETL, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,347 +2701,347 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=61c52ac26fe3b63f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
+          <t>https://www.indeed.com/viewjob?jk=acfe24562dfa1c33</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Backend Engineer, IoT Architecture &amp; Migration</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rakuten Global</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=428d030a371efde6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. FSE Engineer (Java/Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5260c6496b06df56</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior AI Systems Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rakuten International</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
+          <t>Software Data Engineering Intern</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Innovation Associates, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Binghamton, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BI DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Temco Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Carson, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
+          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Backend)</t>
+          <t>Infrastructure Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Frontend Architect</t>
+          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
+          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Frontend Architect</t>
+          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
+          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevSecOps Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9dc833901dbedff</t>
+          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Engineer - Direct Hire Only, no Corp-2-Corp</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pistevo Decision</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60fbf6be4c551ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ITSM Service Now Team</t>
+          <t>Senior Data Engineer - Paradox Machines</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Infinity</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
+          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Scala, Kafka, PostgreSQL, Data Modeling, ETL, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c52ac26fe3b63f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>University of Tennessee Health Science Center</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,59 +3226,59 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfe24562dfa1c33</t>
+          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Backend Engineer, IoT Architecture &amp; Migration</t>
+          <t>AWS Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=428d030a371efde6</t>
+          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,29 +3286,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (DevOps)</t>
+          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Greater Anesthesia Solutions</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
+          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36cf23d5a5bdc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Data Architect - Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Scala, Snowflake, Data Modeling, Terraform, CloudWatch</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=7be41efb52cec9d7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Appmericans team</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Back Market</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=124a5f3483513bd6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Context Layer Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Context Layer Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
+          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Paradox Machines</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,540 +3531,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Everseen</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>University of Tennessee Health Science Center</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>University of Tennessee</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>AWS Data &amp; AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Cupertino, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Greater Anesthesia Solutions</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Architect - Snowflake &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>J2B GLOBAL LLC</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Scala, Snowflake, Data Modeling, Terraform, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7be41efb52cec9d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Cloud Data Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93a7f97444948657</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>.Net developer (strong Azure)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Stier Solutions Inc</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Sherwin-Williams</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Context Layer Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Context Layer Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e198e6ac2972e7f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=306f0bd44cd0eb2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>NAVA TECH LLC</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Data Modeling, ETL, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=66b1fb657f32bd19</t>
         </is>

--- a/results/job_matches_2026-09-04.xlsx
+++ b/results/job_matches_2026-09-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Developer with AI</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Google Cloud Platform, Dataflow, HBase, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad70f5252874459</t>
+          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
         </is>
       </c>
     </row>
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
+          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f362c9602042b5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb65efe8a988bc77</t>
+          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cea54622c0ce7d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Software Engineer - AI Quality and Productivity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wyoming, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
+          <t>https://www.indeed.com/viewjob?jk=639ed0412b5015c8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Quality and Productivity</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
+          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataBricks Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DataBricks Data Engineer</t>
+          <t>Technical Architect - Boomi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
+          <t>https://www.indeed.com/viewjob?jk=b63dd269336a90eb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Technical Architect - Boomi</t>
+          <t>Boomi Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63dd269336a90eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a701b23e34d3c27b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Boomi Engineer - Senior Consultant</t>
+          <t>Software Engineer Consultant II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a701b23e34d3c27b</t>
+          <t>https://www.indeed.com/viewjob?jk=a34c6d42c8ceedf1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91a79069b7b6c23</t>
+          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Engineer, Data Automation and AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
+          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>System Engineer, Data Automation and AI</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Systems Analyst - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Rialto Capital</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe46512a7712cf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Systems Analyst - Remote</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rialto Capital</t>
+          <t>Department of Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MySQL, Data Modeling, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe46512a7712cf</t>
+          <t>https://www.indeed.com/viewjob?jk=800ccaff6ff582aa</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
         </is>
       </c>
     </row>
@@ -1261,29 +1261,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
+          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Data &amp; Reporting Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Medvantx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
+          <t>https://www.indeed.com/viewjob?jk=7488e999f8058bf0</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Databricks Architect (Onsite Hybrid)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,52 +1396,52 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323ab8f6158c9d11</t>
+          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
+          <t>https://www.indeed.com/viewjob?jk=323ab8f6158c9d11</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>International Community Health Services</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EMR, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fdae74ac4398f4</t>
+          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I – SRE</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>International Community Health Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>EMR, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=21fdae74ac4398f4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Customer AI Analytics</t>
+          <t>Senior Cloud Ops Engineer I – SRE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
+          <t>https://www.indeed.com/viewjob?jk=18ffdd5eef1958d3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,242 +1791,242 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a599be99d023bcc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7452d97c75af8dc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
+          <t>https://www.indeed.com/viewjob?jk=f0020bbdb6ae8cba</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
+          <t>https://www.indeed.com/viewjob?jk=69f9a0ce557bd0b4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
+          <t>https://www.indeed.com/viewjob?jk=b00da2a69a1c8752</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
+          <t>https://www.indeed.com/viewjob?jk=2da011c549fe5788</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ee9bf2ddf6f37b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer, Payment Data Intelligence</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TikTok USDS JV</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f8298a7d1edc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Office-Based in Minnesota</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,137 +2071,137 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8abd386f3997679</t>
+          <t>https://www.indeed.com/viewjob?jk=a599be99d023bcc4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a155cddb69c0b0</t>
+          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medina Talent Group </t>
+          <t>STATE WATER RESOURCES CONTROL BOARD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
+          <t>https://www.indeed.com/viewjob?jk=6c7f66e1ab99075a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
+          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rakuten Global</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rakuten International</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
+          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
+          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
+          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BI DevOps Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Temco Logistics</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Carson, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
+          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Data Engineer, Payment Data Intelligence</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
+          <t>https://www.indeed.com/viewjob?jk=95f8298a7d1edc2e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Data Engineer - Office-Based in Minnesota</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8abd386f3997679</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a155cddb69c0b0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Backend)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Oracle, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,137 +2456,137 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b006836fd5da0fd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Frontend Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t xml:space="preserve">Medina Talent Group </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
+          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Frontend Architect</t>
+          <t>Data Engineer (DataLake to AWS)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Supply Chain Data Analytics</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Newell Brands</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
+          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Engineer - Direct Hire Only, no Corp-2-Corp</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pistevo Decision</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60fbf6be4c551ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d07f9859bf5d647a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ITSM Service Now Team</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Rakuten Global</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Rakuten International</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
+          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer</t>
+          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Scala, Kafka, PostgreSQL, Data Modeling, ETL, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c52ac26fe3b63f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>BI DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Temco Logistics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Carson, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfe24562dfa1c33</t>
+          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Backend Engineer, IoT Architecture &amp; Migration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=428d030a371efde6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
+          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI Systems Engineer</t>
+          <t>Senior Analytics Engineer, Product Analytics</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
+          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Data Engineering Intern</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Innovation Associates, Inc.</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Binghamton, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
+          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (DevOps)</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,137 +2946,137 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Frontend Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
+          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Frontend Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Analyst, Supply Chain Data Analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Newell Brands</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - ITSM Service Now Team</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
+          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Paradox Machines</t>
+          <t>Associate, Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>Scala, Kafka, PostgreSQL, Data Modeling, ETL, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
+          <t>https://www.indeed.com/viewjob?jk=61c52ac26fe3b63f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Engineer, IoT Architecture &amp; Migration</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
+          <t>https://www.indeed.com/viewjob?jk=428d030a371efde6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
+          <t>Senior AI Systems Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>University of Tennessee Health Science Center</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Data &amp; AI Platform Engineer</t>
+          <t>Software Data Engineering Intern</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Innovation Associates, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Binghamton, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
+          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Greater Anesthesia Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Infrastructure Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36cf23d5a5bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect - Snowflake &amp; AWS</t>
+          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Scala, Snowflake, Data Modeling, Terraform, CloudWatch</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be41efb52cec9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Appmericans team</t>
+          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Back Market</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git, Datadog</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124a5f3483513bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Context Layer Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
+          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Context Layer Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,367 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66b1fb657f32bd19</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Paradox Machines</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Infinity</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Everseen</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AWS Data &amp; AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Greater Anesthesia Solutions</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f36cf23d5a5bdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sr Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ELEVI Associates, LLC</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Annapolis Junction, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ea53ce383b5d2a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appmericans team</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Back Market</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=124a5f3483513bd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Engineering Associate – CIB Operations Technology</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, PostgreSQL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2a800957b21a8f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Context Layer Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-04.xlsx
+++ b/results/job_matches_2026-09-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1000000882.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
+          <t>Software Engineer, II - Data Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, ECS, Data Factory, Databricks, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7843267cf992ea15</t>
+          <t>https://www.indeed.com/viewjob?jk=2aeb88d99c11a926</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1000000881.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
+          <t>1000000882.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a34457b20435ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=7843267cf992ea15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>1000000881.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a34457b20435ae3</t>
         </is>
       </c>
     </row>
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
+          <t>https://www.indeed.com/viewjob?jk=6513b42373e43b0d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,69 +626,69 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b471c305e99cc22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4723cbe97840a8b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cea54622c0ce7d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cea54622c0ce7d</t>
+          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
         </is>
       </c>
     </row>
@@ -858,47 +858,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>ZipLiens</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=3205953035ac9b3a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DataBricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
+          <t>https://www.indeed.com/viewjob?jk=ac9facab44a0c8e5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Technical Architect - Boomi</t>
+          <t>DataBricks Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63dd269336a90eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Boomi Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer (Backend Java)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>VAMS Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a701b23e34d3c27b</t>
+          <t>https://www.indeed.com/viewjob?jk=eef8a6f3c1b852a1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer Consultant II</t>
+          <t>Technical Architect - Boomi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,129 +1021,129 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34c6d42c8ceedf1</t>
+          <t>https://www.indeed.com/viewjob?jk=b63dd269336a90eb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Boomi Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
+          <t>https://www.indeed.com/viewjob?jk=a701b23e34d3c27b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>System Engineer, Data Automation and AI</t>
+          <t>Software Engineer Consultant II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=a34c6d42c8ceedf1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Backend Java Developer, Officer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd96fe08a5ed3c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Systems Analyst - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rialto Capital</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, IAM, RDS, GCP, BigQuery, Cloud Storage, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe46512a7712cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7757978021f6f0be</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>System Engineer, Data Automation and AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Department of Technology</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MySQL, Data Modeling, Power BI, Splunk</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=800ccaff6ff582aa</t>
+          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Event Network, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
+          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Data Architect Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inter-American Development Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, ETL, Talend, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=c79c054898d0f4e7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Reporting Engineer</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Medvantx</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488e999f8058bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=529f4202718cbb5d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Data &amp; Reporting Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Medvantx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=7488e999f8058bf0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
+          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9668a782d26f23f2</t>
+          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80fb7f5a0962d33</t>
+          <t>https://www.indeed.com/viewjob?jk=9668a782d26f23f2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c80fb7f5a0962d33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
+          <t>https://www.indeed.com/viewjob?jk=40e8117ce12171ea</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
+          <t>https://www.indeed.com/viewjob?jk=69a1db356a25690b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164a25d06b797701</t>
+          <t>https://www.indeed.com/viewjob?jk=9a78908866a9549b</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I – SRE</t>
+          <t>Sr Data Developer (ETL)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>ExcelaCom</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5045c5aee57e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4dea835950a7f8</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0019cb84ac3bc92</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a599be99d023bcc4</t>
+          <t>https://www.indeed.com/viewjob?jk=66c47c01ec242b5c</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
+          <t>https://www.indeed.com/viewjob?jk=be4df5dec943b09f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>STATE WATER RESOURCES CONTROL BOARD</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c7f66e1ab99075a</t>
+          <t>https://www.indeed.com/viewjob?jk=89bdfabc1efc886f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
+          <t>https://www.indeed.com/viewjob?jk=a599be99d023bcc4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
+          <t>https://www.indeed.com/viewjob?jk=815dd91d37507aac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>STATE WATER RESOURCES CONTROL BOARD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,139 +2271,139 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c7f66e1ab99075a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
+          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer, Payment Data Intelligence</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TikTok USDS JV</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f8298a7d1edc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Office-Based in Minnesota</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8abd386f3997679</t>
+          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a155cddb69c0b0</t>
+          <t>https://www.indeed.com/viewjob?jk=16b71269af0f17c5</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medina Talent Group </t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
+          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer (DataLake to AWS)</t>
+          <t>Data Engineer, Payment Data Intelligence</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
+          <t>https://www.indeed.com/viewjob?jk=95f8298a7d1edc2e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Data Engineer - Office-Based in Minnesota</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,29 +2551,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
+          <t>https://www.indeed.com/viewjob?jk=f8abd386f3997679</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Persistent Systems</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07f9859bf5d647a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a155cddb69c0b0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rakuten Global</t>
+          <t xml:space="preserve">Medina Talent Group </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Kafka, Kafka Connect, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer (DataLake to AWS)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rakuten International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
+          <t>https://www.indeed.com/viewjob?jk=075bcb7fa07a9e22</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BI DevOps Engineer</t>
+          <t>Senior Business Intelligence &amp; Automation Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Temco Logistics</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Carson, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
+          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Function Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
+          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
+          <t>https://www.indeed.com/viewjob?jk=d07f9859bf5d647a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Product Analytics</t>
+          <t>Software Engineer III (Java/Python/AWS)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,164 +2841,164 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2c218f1db2c299ce</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Rakuten Global</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bfadcb3e3c8e3d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Rakuten International</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
+          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Senior Software Engineer - San Diego, CA - 2388088</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
+          <t>https://www.indeed.com/viewjob?jk=bf0e9e9d4c63fd83</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Frontend Architect</t>
+          <t>BI DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Temco Logistics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Carson, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>Azure, Databricks, Data Lake Storage, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f491eb42bedb4e44</t>
+          <t>https://www.indeed.com/viewjob?jk=d35943967744e800</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Frontend Architect</t>
+          <t>Big Data Engineer (Hortonworks HDP/HDF)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, YARN, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, Google Cloud Platform, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da58ede475945c92</t>
+          <t>https://www.indeed.com/viewjob?jk=4959e0a53e034434</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Supply Chain Data Analytics</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Newell Brands</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ITSM Service Now Team</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
+          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, AI &amp; Agents</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Appnovation Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Scala, Kafka, PostgreSQL, Data Modeling, ETL, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c52ac26fe3b63f</t>
+          <t>https://www.indeed.com/viewjob?jk=eec062974a4f7b14</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Backend Engineer, IoT Architecture &amp; Migration</t>
+          <t>Ecommerce Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Johnson Health Tech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cottage Grove, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=428d030a371efde6</t>
+          <t>https://www.indeed.com/viewjob?jk=39c33a70af0afdb7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AI Systems Engineer</t>
+          <t>Summer 2027 Feature Engineer Internship</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Snowflake, ETL, ELT, Splunk, DataOps, MLOps, pytest</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Data Engineering Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Innovation Associates, Inc.</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Binghamton, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, ETL, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer, Product Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>RDS, Databricks, Spark, Scala, ETL, CI/CD, GitHub Actions, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
+          <t>https://www.indeed.com/viewjob?jk=b4011591b5f453d2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Analyst, Supply Chain Data Analytics</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Newell Brands</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (DevOps)</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
+          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e939ac0ffe070e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>Allegiant Air</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Systems Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Kinesis, IAM, Azure, GCP, Kafka, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb4e5e009287f5e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Data Engineering Intern</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Innovation Associates, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Binghamton, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
+          <t>https://www.indeed.com/viewjob?jk=afd89a6170ec744a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Paradox Machines</t>
+          <t>Infrastructure Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
+          <t>https://www.indeed.com/viewjob?jk=d341676c031de064</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,24 +3601,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
+          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AWS Data &amp; AI Platform Engineer</t>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5489882ff02a2e52</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java) - Onsite Hybrid</t>
+          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Greater Anesthesia Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5221782b3df25e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer (AWS) Cloud Anesthesia Billing</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Greater Anesthesia Solutions</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, IAM, RDS, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b5589d9617bb262</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36cf23d5a5bdc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>ELEVI Associates, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36cf23d5a5bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea53ce383b5d2a5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Senior Software Engineer - Appmericans team</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ELEVI Associates, LLC</t>
+          <t>Back Market</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,112 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea53ce383b5d2a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appmericans team</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Back Market</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=124a5f3483513bd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Engineering Associate – CIB Operations Technology</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a800957b21a8f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Context Layer Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
         </is>
       </c>
     </row>
